--- a/RoboMME Results — 4 policies (by suite).xlsx
+++ b/RoboMME Results — 4 policies (by suite).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Per-Episode" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Episode" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Per-Episode'!$A$2:$BA$66</definedName>
@@ -1143,6 +1143,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1461,6 +1711,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1779,6 +2279,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2097,6 +2847,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2415,6 +3415,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2733,6 +3983,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3051,6 +4551,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3369,6 +5119,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3687,6 +5687,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4005,6 +6255,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -4323,6 +6823,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>scene_error</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4641,6 +7391,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -4959,6 +7959,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5277,6 +8527,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>timeout</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -5595,6 +9095,256 @@
           <t>thu</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AN60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5911,6 +9661,256 @@
       <c r="C64" s="5" t="inlineStr">
         <is>
           <t>thu</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AN64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>fail</t>
         </is>
       </c>
     </row>
@@ -6102,29 +10102,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D4">
-        <f>IF(COUNTA('Per-Episode'!$D$4:$BA$4)=0,"",COUNTIF('Per-Episode'!$D$4:$BA$4,"success"))</f>
-        <v/>
-      </c>
-      <c r="E4">
-        <f>IF(COUNTA('Per-Episode'!$D$4:$BA$4)=0,"",COUNTIF('Per-Episode'!$D$4:$BA$4,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F4">
-        <f>IF(COUNTA('Per-Episode'!$D$4:$BA$4)=0,"",COUNTIF('Per-Episode'!$D$4:$BA$4,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>IF(COUNTA('Per-Episode'!$D$4:$BA$4)=0,"",COUNTIF('Per-Episode'!$D$4:$BA$4,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H4">
-        <f>IF(COUNTA('Per-Episode'!$D$4:$BA$4)=0,"",COUNTA('Per-Episode'!$D$4:$BA$4))</f>
-        <v/>
-      </c>
-      <c r="I4" s="6">
-        <f>IF($H$4="","",$D$4/$H$4)</f>
-        <v/>
+      <c r="D4" t="n">
+        <v>33</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.66</v>
       </c>
     </row>
     <row r="5">
@@ -6266,29 +10260,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D8">
-        <f>IF(COUNTA('Per-Episode'!$D$8:$BA$8)=0,"",COUNTIF('Per-Episode'!$D$8:$BA$8,"success"))</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>IF(COUNTA('Per-Episode'!$D$8:$BA$8)=0,"",COUNTIF('Per-Episode'!$D$8:$BA$8,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F8">
-        <f>IF(COUNTA('Per-Episode'!$D$8:$BA$8)=0,"",COUNTIF('Per-Episode'!$D$8:$BA$8,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>IF(COUNTA('Per-Episode'!$D$8:$BA$8)=0,"",COUNTIF('Per-Episode'!$D$8:$BA$8,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>IF(COUNTA('Per-Episode'!$D$8:$BA$8)=0,"",COUNTA('Per-Episode'!$D$8:$BA$8))</f>
-        <v/>
-      </c>
-      <c r="I8" s="6">
-        <f>IF($H$8="","",$D$8/$H$8)</f>
-        <v/>
+      <c r="D8" t="n">
+        <v>48</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>50</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="9">
@@ -6430,29 +10418,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D12">
-        <f>IF(COUNTA('Per-Episode'!$D$12:$BA$12)=0,"",COUNTIF('Per-Episode'!$D$12:$BA$12,"success"))</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>IF(COUNTA('Per-Episode'!$D$12:$BA$12)=0,"",COUNTIF('Per-Episode'!$D$12:$BA$12,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F12">
-        <f>IF(COUNTA('Per-Episode'!$D$12:$BA$12)=0,"",COUNTIF('Per-Episode'!$D$12:$BA$12,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>IF(COUNTA('Per-Episode'!$D$12:$BA$12)=0,"",COUNTIF('Per-Episode'!$D$12:$BA$12,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>IF(COUNTA('Per-Episode'!$D$12:$BA$12)=0,"",COUNTA('Per-Episode'!$D$12:$BA$12))</f>
-        <v/>
-      </c>
-      <c r="I12" s="6">
-        <f>IF($H$12="","",$D$12/$H$12)</f>
-        <v/>
+      <c r="D12" t="n">
+        <v>47</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -6594,29 +10576,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D16">
-        <f>IF(COUNTA('Per-Episode'!$D$16:$BA$16)=0,"",COUNTIF('Per-Episode'!$D$16:$BA$16,"success"))</f>
-        <v/>
-      </c>
-      <c r="E16">
-        <f>IF(COUNTA('Per-Episode'!$D$16:$BA$16)=0,"",COUNTIF('Per-Episode'!$D$16:$BA$16,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F16">
-        <f>IF(COUNTA('Per-Episode'!$D$16:$BA$16)=0,"",COUNTIF('Per-Episode'!$D$16:$BA$16,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G16">
-        <f>IF(COUNTA('Per-Episode'!$D$16:$BA$16)=0,"",COUNTIF('Per-Episode'!$D$16:$BA$16,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H16">
-        <f>IF(COUNTA('Per-Episode'!$D$16:$BA$16)=0,"",COUNTA('Per-Episode'!$D$16:$BA$16))</f>
-        <v/>
-      </c>
-      <c r="I16" s="6">
-        <f>IF($H$16="","",$D$16/$H$16)</f>
-        <v/>
+      <c r="D16" t="n">
+        <v>37</v>
+      </c>
+      <c r="E16" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>50</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="17">
@@ -6750,29 +10726,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D20" s="7">
-        <f>IF(SUM($H$4,$H$8,$H$12,$H$16)=0,"",SUM($D$4,$D$8,$D$12,$D$16))</f>
-        <v/>
-      </c>
-      <c r="E20" s="7">
-        <f>IF(SUM($H$4,$H$8,$H$12,$H$16)=0,"",SUM($E$4,$E$8,$E$12,$E$16))</f>
-        <v/>
-      </c>
-      <c r="F20" s="7">
-        <f>IF(SUM($H$4,$H$8,$H$12,$H$16)=0,"",SUM($F$4,$F$8,$F$12,$F$16))</f>
-        <v/>
-      </c>
-      <c r="G20" s="7">
-        <f>IF(SUM($H$4,$H$8,$H$12,$H$16)=0,"",SUM($G$4,$G$8,$G$12,$G$16))</f>
-        <v/>
-      </c>
-      <c r="H20" s="7">
-        <f>IF(SUM($H$4,$H$8,$H$12,$H$16)=0,"",SUM($H$4,$H$8,$H$12,$H$16))</f>
-        <v/>
-      </c>
-      <c r="I20" s="9">
-        <f>IF($H$20="","",$D$20/$H$20)</f>
-        <v/>
+      <c r="D20" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>0.825</v>
       </c>
     </row>
     <row r="21">
@@ -6906,29 +10876,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D24">
-        <f>IF(COUNTA('Per-Episode'!$D$20:$BA$20)=0,"",COUNTIF('Per-Episode'!$D$20:$BA$20,"success"))</f>
-        <v/>
-      </c>
-      <c r="E24">
-        <f>IF(COUNTA('Per-Episode'!$D$20:$BA$20)=0,"",COUNTIF('Per-Episode'!$D$20:$BA$20,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F24">
-        <f>IF(COUNTA('Per-Episode'!$D$20:$BA$20)=0,"",COUNTIF('Per-Episode'!$D$20:$BA$20,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G24">
-        <f>IF(COUNTA('Per-Episode'!$D$20:$BA$20)=0,"",COUNTIF('Per-Episode'!$D$20:$BA$20,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H24">
-        <f>IF(COUNTA('Per-Episode'!$D$20:$BA$20)=0,"",COUNTA('Per-Episode'!$D$20:$BA$20))</f>
-        <v/>
-      </c>
-      <c r="I24" s="6">
-        <f>IF($H$24="","",$D$24/$H$24)</f>
-        <v/>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="n">
+        <v>40</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>50</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="25">
@@ -7070,29 +11034,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D28">
-        <f>IF(COUNTA('Per-Episode'!$D$24:$BA$24)=0,"",COUNTIF('Per-Episode'!$D$24:$BA$24,"success"))</f>
-        <v/>
-      </c>
-      <c r="E28">
-        <f>IF(COUNTA('Per-Episode'!$D$24:$BA$24)=0,"",COUNTIF('Per-Episode'!$D$24:$BA$24,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F28">
-        <f>IF(COUNTA('Per-Episode'!$D$24:$BA$24)=0,"",COUNTIF('Per-Episode'!$D$24:$BA$24,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G28">
-        <f>IF(COUNTA('Per-Episode'!$D$24:$BA$24)=0,"",COUNTIF('Per-Episode'!$D$24:$BA$24,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H28">
-        <f>IF(COUNTA('Per-Episode'!$D$24:$BA$24)=0,"",COUNTA('Per-Episode'!$D$24:$BA$24))</f>
-        <v/>
-      </c>
-      <c r="I28" s="6">
-        <f>IF($H$28="","",$D$28/$H$28)</f>
-        <v/>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>40</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>50</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="29">
@@ -7234,29 +11192,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D32">
-        <f>IF(COUNTA('Per-Episode'!$D$28:$BA$28)=0,"",COUNTIF('Per-Episode'!$D$28:$BA$28,"success"))</f>
-        <v/>
-      </c>
-      <c r="E32">
-        <f>IF(COUNTA('Per-Episode'!$D$28:$BA$28)=0,"",COUNTIF('Per-Episode'!$D$28:$BA$28,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F32">
-        <f>IF(COUNTA('Per-Episode'!$D$28:$BA$28)=0,"",COUNTIF('Per-Episode'!$D$28:$BA$28,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G32">
-        <f>IF(COUNTA('Per-Episode'!$D$28:$BA$28)=0,"",COUNTIF('Per-Episode'!$D$28:$BA$28,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H32">
-        <f>IF(COUNTA('Per-Episode'!$D$28:$BA$28)=0,"",COUNTA('Per-Episode'!$D$28:$BA$28))</f>
-        <v/>
-      </c>
-      <c r="I32" s="6">
-        <f>IF($H$32="","",$D$32/$H$32)</f>
-        <v/>
+      <c r="D32" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>41</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>50</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="33">
@@ -7398,29 +11350,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D36">
-        <f>IF(COUNTA('Per-Episode'!$D$32:$BA$32)=0,"",COUNTIF('Per-Episode'!$D$32:$BA$32,"success"))</f>
-        <v/>
-      </c>
-      <c r="E36">
-        <f>IF(COUNTA('Per-Episode'!$D$32:$BA$32)=0,"",COUNTIF('Per-Episode'!$D$32:$BA$32,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F36">
-        <f>IF(COUNTA('Per-Episode'!$D$32:$BA$32)=0,"",COUNTIF('Per-Episode'!$D$32:$BA$32,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G36">
-        <f>IF(COUNTA('Per-Episode'!$D$32:$BA$32)=0,"",COUNTIF('Per-Episode'!$D$32:$BA$32,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H36">
-        <f>IF(COUNTA('Per-Episode'!$D$32:$BA$32)=0,"",COUNTA('Per-Episode'!$D$32:$BA$32))</f>
-        <v/>
-      </c>
-      <c r="I36" s="6">
-        <f>IF($H$36="","",$D$36/$H$36)</f>
-        <v/>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="n">
+        <v>33</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>50</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="37">
@@ -7554,29 +11500,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D40" s="7">
-        <f>IF(SUM($H$24,$H$28,$H$32,$H$36)=0,"",SUM($D$24,$D$28,$D$32,$D$36))</f>
-        <v/>
-      </c>
-      <c r="E40" s="7">
-        <f>IF(SUM($H$24,$H$28,$H$32,$H$36)=0,"",SUM($E$24,$E$28,$E$32,$E$36))</f>
-        <v/>
-      </c>
-      <c r="F40" s="7">
-        <f>IF(SUM($H$24,$H$28,$H$32,$H$36)=0,"",SUM($F$24,$F$28,$F$32,$F$36))</f>
-        <v/>
-      </c>
-      <c r="G40" s="7">
-        <f>IF(SUM($H$24,$H$28,$H$32,$H$36)=0,"",SUM($G$24,$G$28,$G$32,$G$36))</f>
-        <v/>
-      </c>
-      <c r="H40" s="7">
-        <f>IF(SUM($H$24,$H$28,$H$32,$H$36)=0,"",SUM($H$24,$H$28,$H$32,$H$36))</f>
-        <v/>
-      </c>
-      <c r="I40" s="9">
-        <f>IF($H$40="","",$D$40/$H$40)</f>
-        <v/>
+      <c r="D40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="41">
@@ -7710,29 +11650,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D44">
-        <f>IF(COUNTA('Per-Episode'!$D$36:$BA$36)=0,"",COUNTIF('Per-Episode'!$D$36:$BA$36,"success"))</f>
-        <v/>
-      </c>
-      <c r="E44">
-        <f>IF(COUNTA('Per-Episode'!$D$36:$BA$36)=0,"",COUNTIF('Per-Episode'!$D$36:$BA$36,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F44">
-        <f>IF(COUNTA('Per-Episode'!$D$36:$BA$36)=0,"",COUNTIF('Per-Episode'!$D$36:$BA$36,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G44">
-        <f>IF(COUNTA('Per-Episode'!$D$36:$BA$36)=0,"",COUNTIF('Per-Episode'!$D$36:$BA$36,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H44">
-        <f>IF(COUNTA('Per-Episode'!$D$36:$BA$36)=0,"",COUNTA('Per-Episode'!$D$36:$BA$36))</f>
-        <v/>
-      </c>
-      <c r="I44" s="6">
-        <f>IF($H$44="","",$D$44/$H$44)</f>
-        <v/>
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" t="n">
+        <v>39</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>50</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="45">
@@ -7874,29 +11808,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D48">
-        <f>IF(COUNTA('Per-Episode'!$D$40:$BA$40)=0,"",COUNTIF('Per-Episode'!$D$40:$BA$40,"success"))</f>
-        <v/>
-      </c>
-      <c r="E48">
-        <f>IF(COUNTA('Per-Episode'!$D$40:$BA$40)=0,"",COUNTIF('Per-Episode'!$D$40:$BA$40,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F48">
-        <f>IF(COUNTA('Per-Episode'!$D$40:$BA$40)=0,"",COUNTIF('Per-Episode'!$D$40:$BA$40,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G48">
-        <f>IF(COUNTA('Per-Episode'!$D$40:$BA$40)=0,"",COUNTIF('Per-Episode'!$D$40:$BA$40,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H48">
-        <f>IF(COUNTA('Per-Episode'!$D$40:$BA$40)=0,"",COUNTA('Per-Episode'!$D$40:$BA$40))</f>
-        <v/>
-      </c>
-      <c r="I48" s="6">
-        <f>IF($H$48="","",$D$48/$H$48)</f>
-        <v/>
+      <c r="D48" t="n">
+        <v>13</v>
+      </c>
+      <c r="E48" t="n">
+        <v>37</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>50</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="49">
@@ -8038,29 +11966,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D52">
-        <f>IF(COUNTA('Per-Episode'!$D$44:$BA$44)=0,"",COUNTIF('Per-Episode'!$D$44:$BA$44,"success"))</f>
-        <v/>
-      </c>
-      <c r="E52">
-        <f>IF(COUNTA('Per-Episode'!$D$44:$BA$44)=0,"",COUNTIF('Per-Episode'!$D$44:$BA$44,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F52">
-        <f>IF(COUNTA('Per-Episode'!$D$44:$BA$44)=0,"",COUNTIF('Per-Episode'!$D$44:$BA$44,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G52">
-        <f>IF(COUNTA('Per-Episode'!$D$44:$BA$44)=0,"",COUNTIF('Per-Episode'!$D$44:$BA$44,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H52">
-        <f>IF(COUNTA('Per-Episode'!$D$44:$BA$44)=0,"",COUNTA('Per-Episode'!$D$44:$BA$44))</f>
-        <v/>
-      </c>
-      <c r="I52" s="6">
-        <f>IF($H$52="","",$D$52/$H$52)</f>
-        <v/>
+      <c r="D52" t="n">
+        <v>29</v>
+      </c>
+      <c r="E52" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="53">
@@ -8202,29 +12124,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D56">
-        <f>IF(COUNTA('Per-Episode'!$D$48:$BA$48)=0,"",COUNTIF('Per-Episode'!$D$48:$BA$48,"success"))</f>
-        <v/>
-      </c>
-      <c r="E56">
-        <f>IF(COUNTA('Per-Episode'!$D$48:$BA$48)=0,"",COUNTIF('Per-Episode'!$D$48:$BA$48,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F56">
-        <f>IF(COUNTA('Per-Episode'!$D$48:$BA$48)=0,"",COUNTIF('Per-Episode'!$D$48:$BA$48,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G56">
-        <f>IF(COUNTA('Per-Episode'!$D$48:$BA$48)=0,"",COUNTIF('Per-Episode'!$D$48:$BA$48,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H56">
-        <f>IF(COUNTA('Per-Episode'!$D$48:$BA$48)=0,"",COUNTA('Per-Episode'!$D$48:$BA$48))</f>
-        <v/>
-      </c>
-      <c r="I56" s="6">
-        <f>IF($H$56="","",$D$56/$H$56)</f>
-        <v/>
+      <c r="D56" t="n">
+        <v>13</v>
+      </c>
+      <c r="E56" t="n">
+        <v>37</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>50</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="57">
@@ -8358,29 +12274,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D60" s="7">
-        <f>IF(SUM($H$44,$H$48,$H$52,$H$56)=0,"",SUM($D$44,$D$48,$D$52,$D$56))</f>
-        <v/>
-      </c>
-      <c r="E60" s="7">
-        <f>IF(SUM($H$44,$H$48,$H$52,$H$56)=0,"",SUM($E$44,$E$48,$E$52,$E$56))</f>
-        <v/>
-      </c>
-      <c r="F60" s="7">
-        <f>IF(SUM($H$44,$H$48,$H$52,$H$56)=0,"",SUM($F$44,$F$48,$F$52,$F$56))</f>
-        <v/>
-      </c>
-      <c r="G60" s="7">
-        <f>IF(SUM($H$44,$H$48,$H$52,$H$56)=0,"",SUM($G$44,$G$48,$G$52,$G$56))</f>
-        <v/>
-      </c>
-      <c r="H60" s="7">
-        <f>IF(SUM($H$44,$H$48,$H$52,$H$56)=0,"",SUM($H$44,$H$48,$H$52,$H$56))</f>
-        <v/>
-      </c>
-      <c r="I60" s="9">
-        <f>IF($H$60="","",$D$60/$H$60)</f>
-        <v/>
+      <c r="D60" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>133</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="I60" s="9" t="n">
+        <v>0.315</v>
       </c>
     </row>
     <row r="61">
@@ -8514,29 +12424,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D64">
-        <f>IF(COUNTA('Per-Episode'!$D$52:$BA$52)=0,"",COUNTIF('Per-Episode'!$D$52:$BA$52,"success"))</f>
-        <v/>
-      </c>
-      <c r="E64">
-        <f>IF(COUNTA('Per-Episode'!$D$52:$BA$52)=0,"",COUNTIF('Per-Episode'!$D$52:$BA$52,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F64">
-        <f>IF(COUNTA('Per-Episode'!$D$52:$BA$52)=0,"",COUNTIF('Per-Episode'!$D$52:$BA$52,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G64">
-        <f>IF(COUNTA('Per-Episode'!$D$52:$BA$52)=0,"",COUNTIF('Per-Episode'!$D$52:$BA$52,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H64">
-        <f>IF(COUNTA('Per-Episode'!$D$52:$BA$52)=0,"",COUNTA('Per-Episode'!$D$52:$BA$52))</f>
-        <v/>
-      </c>
-      <c r="I64" s="6">
-        <f>IF($H$64="","",$D$64/$H$64)</f>
-        <v/>
+      <c r="D64" t="n">
+        <v>42</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" t="n">
+        <v>5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>50</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="65">
@@ -8678,29 +12582,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D68">
-        <f>IF(COUNTA('Per-Episode'!$D$56:$BA$56)=0,"",COUNTIF('Per-Episode'!$D$56:$BA$56,"success"))</f>
-        <v/>
-      </c>
-      <c r="E68">
-        <f>IF(COUNTA('Per-Episode'!$D$56:$BA$56)=0,"",COUNTIF('Per-Episode'!$D$56:$BA$56,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F68">
-        <f>IF(COUNTA('Per-Episode'!$D$56:$BA$56)=0,"",COUNTIF('Per-Episode'!$D$56:$BA$56,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G68">
-        <f>IF(COUNTA('Per-Episode'!$D$56:$BA$56)=0,"",COUNTIF('Per-Episode'!$D$56:$BA$56,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H68">
-        <f>IF(COUNTA('Per-Episode'!$D$56:$BA$56)=0,"",COUNTA('Per-Episode'!$D$56:$BA$56))</f>
-        <v/>
-      </c>
-      <c r="I68" s="6">
-        <f>IF($H$68="","",$D$68/$H$68)</f>
-        <v/>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16</v>
+      </c>
+      <c r="F68" t="n">
+        <v>34</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>50</v>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -8842,29 +12740,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D72">
-        <f>IF(COUNTA('Per-Episode'!$D$60:$BA$60)=0,"",COUNTIF('Per-Episode'!$D$60:$BA$60,"success"))</f>
-        <v/>
-      </c>
-      <c r="E72">
-        <f>IF(COUNTA('Per-Episode'!$D$60:$BA$60)=0,"",COUNTIF('Per-Episode'!$D$60:$BA$60,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F72">
-        <f>IF(COUNTA('Per-Episode'!$D$60:$BA$60)=0,"",COUNTIF('Per-Episode'!$D$60:$BA$60,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G72">
-        <f>IF(COUNTA('Per-Episode'!$D$60:$BA$60)=0,"",COUNTIF('Per-Episode'!$D$60:$BA$60,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H72">
-        <f>IF(COUNTA('Per-Episode'!$D$60:$BA$60)=0,"",COUNTA('Per-Episode'!$D$60:$BA$60))</f>
-        <v/>
-      </c>
-      <c r="I72" s="6">
-        <f>IF($H$72="","",$D$72/$H$72)</f>
-        <v/>
+      <c r="D72" t="n">
+        <v>21</v>
+      </c>
+      <c r="E72" t="n">
+        <v>29</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>50</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="73">
@@ -9006,29 +12898,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D76">
-        <f>IF(COUNTA('Per-Episode'!$D$64:$BA$64)=0,"",COUNTIF('Per-Episode'!$D$64:$BA$64,"success"))</f>
-        <v/>
-      </c>
-      <c r="E76">
-        <f>IF(COUNTA('Per-Episode'!$D$64:$BA$64)=0,"",COUNTIF('Per-Episode'!$D$64:$BA$64,"fail"))</f>
-        <v/>
-      </c>
-      <c r="F76">
-        <f>IF(COUNTA('Per-Episode'!$D$64:$BA$64)=0,"",COUNTIF('Per-Episode'!$D$64:$BA$64,"timeout"))</f>
-        <v/>
-      </c>
-      <c r="G76">
-        <f>IF(COUNTA('Per-Episode'!$D$64:$BA$64)=0,"",COUNTIF('Per-Episode'!$D$64:$BA$64,"scene_error"))</f>
-        <v/>
-      </c>
-      <c r="H76">
-        <f>IF(COUNTA('Per-Episode'!$D$64:$BA$64)=0,"",COUNTA('Per-Episode'!$D$64:$BA$64))</f>
-        <v/>
-      </c>
-      <c r="I76" s="6">
-        <f>IF($H$76="","",$D$76/$H$76)</f>
-        <v/>
+      <c r="D76" t="n">
+        <v>15</v>
+      </c>
+      <c r="E76" t="n">
+        <v>35</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>50</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="77">
@@ -9162,29 +13048,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D80" s="7">
-        <f>IF(SUM($H$64,$H$68,$H$72,$H$76)=0,"",SUM($D$64,$D$68,$D$72,$D$76))</f>
-        <v/>
-      </c>
-      <c r="E80" s="7">
-        <f>IF(SUM($H$64,$H$68,$H$72,$H$76)=0,"",SUM($E$64,$E$68,$E$72,$E$76))</f>
-        <v/>
-      </c>
-      <c r="F80" s="7">
-        <f>IF(SUM($H$64,$H$68,$H$72,$H$76)=0,"",SUM($F$64,$F$68,$F$72,$F$76))</f>
-        <v/>
-      </c>
-      <c r="G80" s="7">
-        <f>IF(SUM($H$64,$H$68,$H$72,$H$76)=0,"",SUM($G$64,$G$68,$G$72,$G$76))</f>
-        <v/>
-      </c>
-      <c r="H80" s="7">
-        <f>IF(SUM($H$64,$H$68,$H$72,$H$76)=0,"",SUM($H$64,$H$68,$H$72,$H$76))</f>
-        <v/>
-      </c>
-      <c r="I80" s="9">
-        <f>IF($H$80="","",$D$80/$H$80)</f>
-        <v/>
+      <c r="D80" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="I80" s="9" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="81">
@@ -9310,29 +13190,23 @@
           <t>thu</t>
         </is>
       </c>
-      <c r="D84" s="10">
-        <f>IF(SUM($H$20,$H$40,$H$60,$H$80)=0,"",SUM($D$20,$D$40,$D$60,$D$80))</f>
-        <v/>
-      </c>
-      <c r="E84" s="10">
-        <f>IF(SUM($H$20,$H$40,$H$60,$H$80)=0,"",SUM($E$20,$E$40,$E$60,$E$80))</f>
-        <v/>
-      </c>
-      <c r="F84" s="10">
-        <f>IF(SUM($H$20,$H$40,$H$60,$H$80)=0,"",SUM($F$20,$F$40,$F$60,$F$80))</f>
-        <v/>
-      </c>
-      <c r="G84" s="10">
-        <f>IF(SUM($H$20,$H$40,$H$60,$H$80)=0,"",SUM($G$20,$G$40,$G$60,$G$80))</f>
-        <v/>
-      </c>
-      <c r="H84" s="10">
-        <f>IF(SUM($H$20,$H$40,$H$60,$H$80)=0,"",SUM($H$20,$H$40,$H$60,$H$80))</f>
-        <v/>
-      </c>
-      <c r="I84" s="12">
-        <f>IF($H$84="","",$D$84/$H$84)</f>
-        <v/>
+      <c r="D84" s="10" t="n">
+        <v>342</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>403</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="G84" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="10" t="n">
+        <v>800</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>0.4275</v>
       </c>
     </row>
     <row r="85">
